--- a/jogos_2025-03-18.xlsx
+++ b/jogos_2025-03-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>Date</t>
   </si>
@@ -127,112 +127,58 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
     <t>16:45</t>
   </si>
   <si>
+    <t>England EFL League One</t>
+  </si>
+  <si>
     <t>Northern Ireland NIFL Premiership</t>
   </si>
   <si>
-    <t>England EFL League One</t>
-  </si>
-  <si>
     <t>2024/2025</t>
   </si>
   <si>
+    <t>Rotherham United</t>
+  </si>
+  <si>
+    <t>Glentoran</t>
+  </si>
+  <si>
     <t>Coleraine</t>
   </si>
   <si>
-    <t>Rotherham United</t>
-  </si>
-  <si>
-    <t>Glentoran</t>
+    <t>Wycombe Wanderers</t>
+  </si>
+  <si>
+    <t>Larne</t>
   </si>
   <si>
     <t>Cliftonville</t>
   </si>
   <si>
-    <t>Wycombe Wanderers</t>
-  </si>
-  <si>
-    <t>Larne</t>
-  </si>
-  <si>
     <t>complete</t>
   </si>
   <si>
+    <t>['66', '90+5']</t>
+  </si>
+  <si>
+    <t>['11', '47']</t>
+  </si>
+  <si>
     <t>['72', '82']</t>
   </si>
   <si>
-    <t>['66', '90+5']</t>
-  </si>
-  <si>
-    <t>['11', '47']</t>
+    <t>['69', '90', '90+2']</t>
+  </si>
+  <si>
+    <t>['59', '66']</t>
   </si>
   <si>
     <t>['66', '87']</t>
-  </si>
-  <si>
-    <t>['69', '90', '90+2']</t>
-  </si>
-  <si>
-    <t>['59', '66']</t>
   </si>
 </sst>
 </file>
@@ -596,10 +542,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD4"/>
+  <dimension ref="A1:AL4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -714,85 +660,31 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45734</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -801,332 +693,224 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="L2">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="M2">
-        <v>3.35</v>
+        <v>3.13</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>2.48</v>
       </c>
       <c r="O2">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="P2">
-        <v>12.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q2">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="R2">
+        <v>1.44</v>
+      </c>
+      <c r="S2">
+        <v>2.63</v>
+      </c>
+      <c r="T2">
+        <v>3.25</v>
+      </c>
+      <c r="U2">
+        <v>1.33</v>
+      </c>
+      <c r="V2">
+        <v>10</v>
+      </c>
+      <c r="W2">
+        <v>1.06</v>
+      </c>
+      <c r="X2">
+        <v>1.06</v>
+      </c>
+      <c r="Y2">
+        <v>8.5</v>
+      </c>
+      <c r="Z2">
         <v>1.35</v>
       </c>
-      <c r="S2">
-        <v>3</v>
-      </c>
-      <c r="T2">
-        <v>2.7</v>
-      </c>
-      <c r="U2">
-        <v>1.44</v>
-      </c>
-      <c r="V2">
+      <c r="AA2">
+        <v>3.1</v>
+      </c>
+      <c r="AB2">
+        <v>1.98</v>
+      </c>
+      <c r="AC2">
+        <v>1.77</v>
+      </c>
+      <c r="AD2">
+        <v>3.65</v>
+      </c>
+      <c r="AE2">
+        <v>1.28</v>
+      </c>
+      <c r="AF2">
+        <v>1.91</v>
+      </c>
+      <c r="AG2">
+        <v>1.91</v>
+      </c>
+      <c r="AH2">
         <v>7</v>
-      </c>
-      <c r="W2">
-        <v>1.1</v>
-      </c>
-      <c r="X2">
-        <v>1</v>
-      </c>
-      <c r="Y2">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z2">
-        <v>1.21</v>
-      </c>
-      <c r="AA2">
-        <v>3.58</v>
-      </c>
-      <c r="AB2">
-        <v>1.75</v>
-      </c>
-      <c r="AC2">
-        <v>1.91</v>
-      </c>
-      <c r="AD2">
-        <v>2.88</v>
-      </c>
-      <c r="AE2">
-        <v>1.32</v>
-      </c>
-      <c r="AF2">
-        <v>1.7</v>
-      </c>
-      <c r="AG2">
-        <v>2.1</v>
-      </c>
-      <c r="AH2">
-        <v>5.4</v>
       </c>
       <c r="AI2">
         <v>1.09</v>
       </c>
       <c r="AJ2" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="AK2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL2">
-        <v>1.25</v>
-      </c>
-      <c r="AM2">
-        <v>1.3</v>
-      </c>
-      <c r="AN2">
-        <v>1.85</v>
-      </c>
-      <c r="AO2">
-        <v>11</v>
-      </c>
-      <c r="AP2">
-        <v>1.28</v>
-      </c>
-      <c r="AQ2">
-        <v>1.6</v>
-      </c>
-      <c r="AR2">
-        <v>1.99</v>
-      </c>
-      <c r="AS2">
-        <v>2.55</v>
-      </c>
-      <c r="AT2">
-        <v>3.42</v>
-      </c>
-      <c r="AU2">
-        <v>3.08</v>
-      </c>
-      <c r="AV2">
-        <v>2.28</v>
-      </c>
-      <c r="AW2">
-        <v>1.8</v>
-      </c>
-      <c r="AX2">
-        <v>1.48</v>
-      </c>
-      <c r="AY2">
-        <v>1.23</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.59</v>
-      </c>
-      <c r="BC2">
-        <v>2.44</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>52</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45734.69791666666</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45734</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="L3">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="M3">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="N3">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="O3">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="P3">
+        <v>5.8</v>
+      </c>
+      <c r="Q3">
+        <v>2.2</v>
+      </c>
+      <c r="R3">
+        <v>1.57</v>
+      </c>
+      <c r="S3">
+        <v>2.25</v>
+      </c>
+      <c r="T3">
+        <v>3.75</v>
+      </c>
+      <c r="U3">
+        <v>1.25</v>
+      </c>
+      <c r="V3">
         <v>8.5</v>
       </c>
-      <c r="Q3">
-        <v>1.8</v>
-      </c>
-      <c r="R3">
-        <v>1.44</v>
-      </c>
-      <c r="S3">
-        <v>2.63</v>
-      </c>
-      <c r="T3">
-        <v>3.25</v>
-      </c>
-      <c r="U3">
-        <v>1.33</v>
-      </c>
-      <c r="V3">
-        <v>10</v>
-      </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="Z3">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AA3">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AB3">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AD3">
-        <v>3.65</v>
+        <v>4.75</v>
       </c>
       <c r="AE3">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH3">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AI3">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AJ3" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AK3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL3">
-        <v>1.57</v>
-      </c>
-      <c r="AM3">
-        <v>1.28</v>
-      </c>
-      <c r="AN3">
-        <v>1.38</v>
-      </c>
-      <c r="AO3">
-        <v>8</v>
-      </c>
-      <c r="AP3">
-        <v>1.29</v>
-      </c>
-      <c r="AQ3">
-        <v>1.5</v>
-      </c>
-      <c r="AR3">
-        <v>1.82</v>
-      </c>
-      <c r="AS3">
-        <v>2.28</v>
-      </c>
-      <c r="AT3">
-        <v>2.9</v>
-      </c>
-      <c r="AU3">
-        <v>3.15</v>
-      </c>
-      <c r="AV3">
-        <v>2.38</v>
-      </c>
-      <c r="AW3">
-        <v>1.86</v>
-      </c>
-      <c r="AX3">
-        <v>1.54</v>
-      </c>
-      <c r="AY3">
-        <v>1.34</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>2.3</v>
-      </c>
-      <c r="BC3">
-        <v>1.8</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>53</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45734.69791666666</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45734</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1135,147 +919,93 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="L4">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="M4">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N4">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="P4">
-        <v>5.8</v>
+        <v>12.75</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="R4">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="S4">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="U4">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="V4">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>5.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z4">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AA4">
-        <v>2.55</v>
+        <v>3.58</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD4">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AF4">
+        <v>1.7</v>
+      </c>
+      <c r="AG4">
         <v>2.1</v>
       </c>
-      <c r="AG4">
-        <v>1.67</v>
-      </c>
       <c r="AH4">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="AI4">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AJ4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="AK4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AL4">
-        <v>1.4</v>
-      </c>
-      <c r="AM4">
-        <v>1.33</v>
-      </c>
-      <c r="AN4">
-        <v>1.47</v>
-      </c>
-      <c r="AO4">
-        <v>5</v>
-      </c>
-      <c r="AP4">
-        <v>1.26</v>
-      </c>
-      <c r="AQ4">
-        <v>1.5</v>
-      </c>
-      <c r="AR4">
-        <v>1.87</v>
-      </c>
-      <c r="AS4">
-        <v>2.42</v>
-      </c>
-      <c r="AT4">
-        <v>3.28</v>
-      </c>
-      <c r="AU4">
-        <v>3.22</v>
-      </c>
-      <c r="AV4">
-        <v>2.28</v>
-      </c>
-      <c r="AW4">
-        <v>1.79</v>
-      </c>
-      <c r="AX4">
-        <v>1.44</v>
-      </c>
-      <c r="AY4">
-        <v>1.25</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.95</v>
-      </c>
-      <c r="BC4">
-        <v>2.2</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>54</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45734.69791666666</v>
       </c>
     </row>

--- a/jogos_2025-03-18.xlsx
+++ b/jogos_2025-03-18.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -787,7 +787,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="P3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AA3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['72', '82']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['66', '87']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.25</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['11', '47']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['59', '66']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45734.69791666666</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -916,7 +916,7 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
-        <v>3.58</v>
+        <v>2.55</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['72', '82']</t>
+          <t>['11', '47']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['66', '87']</t>
+          <t>['59', '66']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45734.69791666666</v>
